--- a/data/trans_bre/P15B_3_R-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/P15B_3_R-Provincia-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-1,79</t>
+          <t>-4,05</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>-15,17%</t>
+          <t>-29,67%</t>
         </is>
       </c>
     </row>
@@ -660,22 +660,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-80,86; -20,16</t>
+          <t>-80,94; -20,36</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-17,01; 11,54</t>
+          <t>-18,39; 10,54</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-31,3; 16,79</t>
+          <t>-30,12; 20,05</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-18,74; 10,56</t>
+          <t>-22,23; 8,01</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -690,12 +690,12 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-78,96; 200,41</t>
+          <t>-74,81; 263,79</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-80,41; 530,87</t>
+          <t>-85,15; 185,68</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-23,22</t>
+          <t>-22,66</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -760,22 +760,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 58,6</t>
+          <t>0,0; 56,27</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-21,65; -2,76</t>
+          <t>-24,0; -2,77</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-26,63; 20,12</t>
+          <t>-26,67; 21,77</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-50,0; -6,81</t>
+          <t>-46,36; -6,13</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-10,36</t>
+          <t>-15,85</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>-45,73%</t>
+          <t>-57,55%</t>
         </is>
       </c>
     </row>
@@ -860,22 +860,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-38,96; -4,62</t>
+          <t>-37,17; -4,71</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-34,7; -12,83</t>
+          <t>-36,04; -14,06</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-37,06; -4,1</t>
+          <t>-39,86; -3,97</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-30,96; 10,13</t>
+          <t>-37,33; 5,01</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 193,54</t>
+          <t>-100,0; 90,97</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-39,56</t>
+          <t>-35,92</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-91,11%</t>
+          <t>-90,49%</t>
         </is>
       </c>
     </row>
@@ -960,22 +960,22 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-51,25; -10,78</t>
+          <t>-51,64; -10,98</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-18,26; 0,0</t>
+          <t>-19,8; 0,0</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-23,32; 6,78</t>
+          <t>-23,13; 6,86</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-69,25; -12,5</t>
+          <t>-64,47; -7,88</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 148,69</t>
+          <t>-100,0; 134,93</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -22,07</t>
+          <t>-100,0; 27,34</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-12,84</t>
+          <t>-13,43</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1060,17 +1060,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-73,03; 14,5</t>
+          <t>-73,91; 15,4</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-60,61; -7,95</t>
+          <t>-60,78; -8,03</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-46,33; 62,92</t>
+          <t>-39,74; 63,88</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>-26,36</t>
+          <t>-24,07</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>-92,91%</t>
+          <t>-92,56%</t>
         </is>
       </c>
     </row>
@@ -1160,32 +1160,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-89,97; -14,34</t>
+          <t>-89,89; -12,12</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-29,79; 7,33</t>
+          <t>-30,28; 6,98</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-33,07; -3,61</t>
+          <t>-31,74; -3,71</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-46,1; -10,92</t>
+          <t>-42,54; -9,53</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 12,84</t>
+          <t>-100,0; -11,08</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-92,11; 89,61</t>
+          <t>-91,27; 91,61</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -42,6</t>
+          <t>-100,0; -45,61</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>-5,21</t>
+          <t>-2,92</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>-32,81%</t>
+          <t>-23,08%</t>
         </is>
       </c>
     </row>
@@ -1260,32 +1260,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-40,54; 14,26</t>
+          <t>-40,09; 15,96</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-49,64; -20,69</t>
+          <t>-47,86; -19,89</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-31,0; 0,88</t>
+          <t>-31,03; -0,02</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-20,92; 7,39</t>
+          <t>-15,16; 7,9</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-82,35; 90,63</t>
+          <t>-82,65; 82,3</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-95,42; -55,91</t>
+          <t>-95,08; -53,21</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -1295,7 +1295,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-75,86; 123,15</t>
+          <t>-72,8; 162,8</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>-18,25</t>
+          <t>-17,88</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>-63,65%</t>
+          <t>-62,98%</t>
         </is>
       </c>
     </row>
@@ -1360,27 +1360,27 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-45,61; -4,58</t>
+          <t>-44,3; -4,21</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-14,32; 26,04</t>
+          <t>-14,01; 30,36</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-11,54; 11,71</t>
+          <t>-11,49; 11,9</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-41,84; 3,39</t>
+          <t>-40,43; 3,54</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 13,83</t>
+          <t>-100,0; 3,94</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -1395,7 +1395,7 @@
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-94,1; 81,34</t>
+          <t>-93,96; 107,08</t>
         </is>
       </c>
     </row>
@@ -1427,7 +1427,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>-15,96</t>
+          <t>-15,38</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1447,7 +1447,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>-68,37%</t>
+          <t>-68,3%</t>
         </is>
       </c>
     </row>
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-32,11; -11,88</t>
+          <t>-32,69; -11,43</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-22,03; -10,97</t>
+          <t>-22,25; -11,08</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-14,04; -1,39</t>
+          <t>-13,35; -1,34</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-24,26; -8,81</t>
+          <t>-23,51; -9,0</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-85,23; -41,38</t>
+          <t>-85,18; -39,09</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-88,9; -56,79</t>
+          <t>-88,49; -56,95</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-74,96; -9,8</t>
+          <t>-73,22; -6,97</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-82,96; -45,4</t>
+          <t>-82,23; -47,18</t>
         </is>
       </c>
     </row>
